--- a/artfynd/A 16081-2026 artfynd.xlsx
+++ b/artfynd/A 16081-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135821154</v>
       </c>
       <c r="B2" t="n">
-        <v>93363</v>
+        <v>93365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135821174</v>
       </c>
       <c r="B4" t="n">
-        <v>97933</v>
+        <v>97935</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>135821189</v>
       </c>
       <c r="B6" t="n">
-        <v>97371</v>
+        <v>97373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135821161</v>
       </c>
       <c r="B12" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>135821168</v>
       </c>
       <c r="B18" t="n">
-        <v>93017</v>
+        <v>93019</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135821158</v>
       </c>
       <c r="B28" t="n">
-        <v>93034</v>
+        <v>93036</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>135821177</v>
       </c>
       <c r="B29" t="n">
-        <v>96694</v>
+        <v>96696</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>135821160</v>
       </c>
       <c r="B30" t="n">
-        <v>87695</v>
+        <v>87697</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 16081-2026 artfynd.xlsx
+++ b/artfynd/A 16081-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135821154</v>
       </c>
       <c r="B2" t="n">
-        <v>93365</v>
+        <v>93380</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135821163</v>
       </c>
       <c r="B3" t="n">
-        <v>78450</v>
+        <v>78452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135821174</v>
       </c>
       <c r="B4" t="n">
-        <v>97935</v>
+        <v>97952</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135821176</v>
       </c>
       <c r="B5" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>135821189</v>
       </c>
       <c r="B6" t="n">
-        <v>97373</v>
+        <v>97390</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135821166</v>
       </c>
       <c r="B7" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>135821173</v>
       </c>
       <c r="B8" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135821170</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>135821175</v>
       </c>
       <c r="B10" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>135821178</v>
       </c>
       <c r="B11" t="n">
-        <v>78800</v>
+        <v>78802</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135821161</v>
       </c>
       <c r="B12" t="n">
-        <v>89428</v>
+        <v>89430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>135821155</v>
       </c>
       <c r="B13" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>135821156</v>
       </c>
       <c r="B14" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>135821179</v>
       </c>
       <c r="B15" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135821157</v>
       </c>
       <c r="B16" t="n">
-        <v>78800</v>
+        <v>78802</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>135821165</v>
       </c>
       <c r="B17" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>135821168</v>
       </c>
       <c r="B18" t="n">
-        <v>93019</v>
+        <v>93034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>135821169</v>
       </c>
       <c r="B19" t="n">
-        <v>41610</v>
+        <v>41612</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>135821180</v>
       </c>
       <c r="B20" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>135821164</v>
       </c>
       <c r="B21" t="n">
-        <v>83433</v>
+        <v>83435</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>135821152</v>
       </c>
       <c r="B22" t="n">
-        <v>83426</v>
+        <v>83428</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>135821159</v>
       </c>
       <c r="B23" t="n">
-        <v>79522</v>
+        <v>79524</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>135821153</v>
       </c>
       <c r="B24" t="n">
-        <v>78800</v>
+        <v>78802</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135821162</v>
       </c>
       <c r="B25" t="n">
-        <v>78800</v>
+        <v>78802</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>135821167</v>
       </c>
       <c r="B26" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>135821171</v>
       </c>
       <c r="B27" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135821158</v>
       </c>
       <c r="B28" t="n">
-        <v>93036</v>
+        <v>93051</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>135821177</v>
       </c>
       <c r="B29" t="n">
-        <v>96696</v>
+        <v>96713</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>135821160</v>
       </c>
       <c r="B30" t="n">
-        <v>87697</v>
+        <v>87699</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 16081-2026 artfynd.xlsx
+++ b/artfynd/A 16081-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135821154</v>
       </c>
       <c r="B2" t="n">
-        <v>93380</v>
+        <v>93381</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135821163</v>
       </c>
       <c r="B3" t="n">
-        <v>78452</v>
+        <v>78453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135821174</v>
       </c>
       <c r="B4" t="n">
-        <v>97952</v>
+        <v>97953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135821176</v>
       </c>
       <c r="B5" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>135821189</v>
       </c>
       <c r="B6" t="n">
-        <v>97390</v>
+        <v>97391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135821166</v>
       </c>
       <c r="B7" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>135821173</v>
       </c>
       <c r="B8" t="n">
-        <v>79602</v>
+        <v>79603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135821170</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>135821175</v>
       </c>
       <c r="B10" t="n">
-        <v>79602</v>
+        <v>79603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>135821178</v>
       </c>
       <c r="B11" t="n">
-        <v>78802</v>
+        <v>78803</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135821161</v>
       </c>
       <c r="B12" t="n">
-        <v>89430</v>
+        <v>89431</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>135821155</v>
       </c>
       <c r="B13" t="n">
-        <v>79602</v>
+        <v>79603</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>135821156</v>
       </c>
       <c r="B14" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>135821179</v>
       </c>
       <c r="B15" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135821157</v>
       </c>
       <c r="B16" t="n">
-        <v>78802</v>
+        <v>78803</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>135821165</v>
       </c>
       <c r="B17" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>135821168</v>
       </c>
       <c r="B18" t="n">
-        <v>93034</v>
+        <v>93035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>135821180</v>
       </c>
       <c r="B20" t="n">
-        <v>79602</v>
+        <v>79603</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>135821164</v>
       </c>
       <c r="B21" t="n">
-        <v>83435</v>
+        <v>83436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>135821152</v>
       </c>
       <c r="B22" t="n">
-        <v>83428</v>
+        <v>83429</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>135821159</v>
       </c>
       <c r="B23" t="n">
-        <v>79524</v>
+        <v>79525</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>135821153</v>
       </c>
       <c r="B24" t="n">
-        <v>78802</v>
+        <v>78803</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135821162</v>
       </c>
       <c r="B25" t="n">
-        <v>78802</v>
+        <v>78803</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>135821167</v>
       </c>
       <c r="B26" t="n">
-        <v>79602</v>
+        <v>79603</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>135821171</v>
       </c>
       <c r="B27" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135821158</v>
       </c>
       <c r="B28" t="n">
-        <v>93051</v>
+        <v>93052</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>135821177</v>
       </c>
       <c r="B29" t="n">
-        <v>96713</v>
+        <v>96714</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>135821160</v>
       </c>
       <c r="B30" t="n">
-        <v>87699</v>
+        <v>87700</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 16081-2026 artfynd.xlsx
+++ b/artfynd/A 16081-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135821154</v>
       </c>
       <c r="B2" t="n">
-        <v>93381</v>
+        <v>93382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135821174</v>
       </c>
       <c r="B4" t="n">
-        <v>97953</v>
+        <v>97954</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>135821189</v>
       </c>
       <c r="B6" t="n">
-        <v>97391</v>
+        <v>97392</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135821161</v>
       </c>
       <c r="B12" t="n">
-        <v>89431</v>
+        <v>89432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>135821168</v>
       </c>
       <c r="B18" t="n">
-        <v>93035</v>
+        <v>93036</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135821158</v>
       </c>
       <c r="B28" t="n">
-        <v>93052</v>
+        <v>93053</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>135821177</v>
       </c>
       <c r="B29" t="n">
-        <v>96714</v>
+        <v>96715</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>135821160</v>
       </c>
       <c r="B30" t="n">
-        <v>87700</v>
+        <v>87701</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 16081-2026 artfynd.xlsx
+++ b/artfynd/A 16081-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135821154</v>
       </c>
       <c r="B2" t="n">
-        <v>93382</v>
+        <v>93383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135821163</v>
       </c>
       <c r="B3" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135821174</v>
       </c>
       <c r="B4" t="n">
-        <v>97954</v>
+        <v>97955</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135821176</v>
       </c>
       <c r="B5" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>135821189</v>
       </c>
       <c r="B6" t="n">
-        <v>97392</v>
+        <v>97393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135821166</v>
       </c>
       <c r="B7" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>135821173</v>
       </c>
       <c r="B8" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135821170</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>135821175</v>
       </c>
       <c r="B10" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>135821178</v>
       </c>
       <c r="B11" t="n">
-        <v>78803</v>
+        <v>78804</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135821161</v>
       </c>
       <c r="B12" t="n">
-        <v>89432</v>
+        <v>89433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>135821155</v>
       </c>
       <c r="B13" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>135821156</v>
       </c>
       <c r="B14" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>135821179</v>
       </c>
       <c r="B15" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135821157</v>
       </c>
       <c r="B16" t="n">
-        <v>78803</v>
+        <v>78804</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>135821165</v>
       </c>
       <c r="B17" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>135821168</v>
       </c>
       <c r="B18" t="n">
-        <v>93036</v>
+        <v>93037</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>135821169</v>
       </c>
       <c r="B19" t="n">
-        <v>41612</v>
+        <v>41613</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>135821180</v>
       </c>
       <c r="B20" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>135821164</v>
       </c>
       <c r="B21" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>135821152</v>
       </c>
       <c r="B22" t="n">
-        <v>83429</v>
+        <v>83430</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>135821159</v>
       </c>
       <c r="B23" t="n">
-        <v>79525</v>
+        <v>79526</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>135821153</v>
       </c>
       <c r="B24" t="n">
-        <v>78803</v>
+        <v>78804</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135821162</v>
       </c>
       <c r="B25" t="n">
-        <v>78803</v>
+        <v>78804</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>135821167</v>
       </c>
       <c r="B26" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>135821171</v>
       </c>
       <c r="B27" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135821158</v>
       </c>
       <c r="B28" t="n">
-        <v>93053</v>
+        <v>93054</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>135821177</v>
       </c>
       <c r="B29" t="n">
-        <v>96715</v>
+        <v>96716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>135821160</v>
       </c>
       <c r="B30" t="n">
-        <v>87701</v>
+        <v>87702</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 16081-2026 artfynd.xlsx
+++ b/artfynd/A 16081-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135821154</v>
       </c>
       <c r="B2" t="n">
-        <v>93383</v>
+        <v>93389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135821163</v>
       </c>
       <c r="B3" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135821174</v>
       </c>
       <c r="B4" t="n">
-        <v>97955</v>
+        <v>97961</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135821176</v>
       </c>
       <c r="B5" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>135821189</v>
       </c>
       <c r="B6" t="n">
-        <v>97393</v>
+        <v>97399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135821166</v>
       </c>
       <c r="B7" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>135821173</v>
       </c>
       <c r="B8" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135821170</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>135821175</v>
       </c>
       <c r="B10" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>135821178</v>
       </c>
       <c r="B11" t="n">
-        <v>78804</v>
+        <v>78808</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135821161</v>
       </c>
       <c r="B12" t="n">
-        <v>89433</v>
+        <v>89439</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>135821155</v>
       </c>
       <c r="B13" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>135821156</v>
       </c>
       <c r="B14" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>135821179</v>
       </c>
       <c r="B15" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135821157</v>
       </c>
       <c r="B16" t="n">
-        <v>78804</v>
+        <v>78808</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>135821165</v>
       </c>
       <c r="B17" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>135821168</v>
       </c>
       <c r="B18" t="n">
-        <v>93037</v>
+        <v>93043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>135821180</v>
       </c>
       <c r="B20" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>135821164</v>
       </c>
       <c r="B21" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>135821152</v>
       </c>
       <c r="B22" t="n">
-        <v>83430</v>
+        <v>83434</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>135821159</v>
       </c>
       <c r="B23" t="n">
-        <v>79526</v>
+        <v>79530</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>135821153</v>
       </c>
       <c r="B24" t="n">
-        <v>78804</v>
+        <v>78808</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135821162</v>
       </c>
       <c r="B25" t="n">
-        <v>78804</v>
+        <v>78808</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>135821167</v>
       </c>
       <c r="B26" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>135821171</v>
       </c>
       <c r="B27" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135821158</v>
       </c>
       <c r="B28" t="n">
-        <v>93054</v>
+        <v>93060</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>135821177</v>
       </c>
       <c r="B29" t="n">
-        <v>96716</v>
+        <v>96722</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>135821160</v>
       </c>
       <c r="B30" t="n">
-        <v>87702</v>
+        <v>87708</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 16081-2026 artfynd.xlsx
+++ b/artfynd/A 16081-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135821154</v>
       </c>
       <c r="B2" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135821163</v>
       </c>
       <c r="B3" t="n">
-        <v>78458</v>
+        <v>78459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135821174</v>
       </c>
       <c r="B4" t="n">
-        <v>97961</v>
+        <v>97962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135821176</v>
       </c>
       <c r="B5" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>135821189</v>
       </c>
       <c r="B6" t="n">
-        <v>97399</v>
+        <v>97400</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135821166</v>
       </c>
       <c r="B7" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>135821173</v>
       </c>
       <c r="B8" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135821170</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>135821175</v>
       </c>
       <c r="B10" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>135821178</v>
       </c>
       <c r="B11" t="n">
-        <v>78808</v>
+        <v>78809</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135821161</v>
       </c>
       <c r="B12" t="n">
-        <v>89439</v>
+        <v>89440</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>135821155</v>
       </c>
       <c r="B13" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>135821156</v>
       </c>
       <c r="B14" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>135821179</v>
       </c>
       <c r="B15" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135821157</v>
       </c>
       <c r="B16" t="n">
-        <v>78808</v>
+        <v>78809</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>135821165</v>
       </c>
       <c r="B17" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>135821168</v>
       </c>
       <c r="B18" t="n">
-        <v>93043</v>
+        <v>93044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>135821180</v>
       </c>
       <c r="B20" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>135821164</v>
       </c>
       <c r="B21" t="n">
-        <v>83441</v>
+        <v>83442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>135821152</v>
       </c>
       <c r="B22" t="n">
-        <v>83434</v>
+        <v>83435</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>135821159</v>
       </c>
       <c r="B23" t="n">
-        <v>79530</v>
+        <v>79531</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>135821153</v>
       </c>
       <c r="B24" t="n">
-        <v>78808</v>
+        <v>78809</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135821162</v>
       </c>
       <c r="B25" t="n">
-        <v>78808</v>
+        <v>78809</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>135821167</v>
       </c>
       <c r="B26" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>135821171</v>
       </c>
       <c r="B27" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135821158</v>
       </c>
       <c r="B28" t="n">
-        <v>93060</v>
+        <v>93061</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>135821177</v>
       </c>
       <c r="B29" t="n">
-        <v>96722</v>
+        <v>96723</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>135821160</v>
       </c>
       <c r="B30" t="n">
-        <v>87708</v>
+        <v>87709</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 16081-2026 artfynd.xlsx
+++ b/artfynd/A 16081-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135821154</v>
       </c>
       <c r="B2" t="n">
-        <v>93390</v>
+        <v>93396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135821163</v>
       </c>
       <c r="B3" t="n">
-        <v>78459</v>
+        <v>78463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135821174</v>
       </c>
       <c r="B4" t="n">
-        <v>97962</v>
+        <v>97973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135821176</v>
       </c>
       <c r="B5" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>135821189</v>
       </c>
       <c r="B6" t="n">
-        <v>97400</v>
+        <v>97411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135821166</v>
       </c>
       <c r="B7" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>135821173</v>
       </c>
       <c r="B8" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135821170</v>
       </c>
       <c r="B9" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>135821175</v>
       </c>
       <c r="B10" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>135821178</v>
       </c>
       <c r="B11" t="n">
-        <v>78809</v>
+        <v>78813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135821161</v>
       </c>
       <c r="B12" t="n">
-        <v>89440</v>
+        <v>89446</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>135821155</v>
       </c>
       <c r="B13" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>135821156</v>
       </c>
       <c r="B14" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>135821179</v>
       </c>
       <c r="B15" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135821157</v>
       </c>
       <c r="B16" t="n">
-        <v>78809</v>
+        <v>78813</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>135821165</v>
       </c>
       <c r="B17" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>135821168</v>
       </c>
       <c r="B18" t="n">
-        <v>93044</v>
+        <v>93050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>135821180</v>
       </c>
       <c r="B20" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>135821164</v>
       </c>
       <c r="B21" t="n">
-        <v>83442</v>
+        <v>83446</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>135821152</v>
       </c>
       <c r="B22" t="n">
-        <v>83435</v>
+        <v>83439</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>135821159</v>
       </c>
       <c r="B23" t="n">
-        <v>79531</v>
+        <v>79535</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>135821153</v>
       </c>
       <c r="B24" t="n">
-        <v>78809</v>
+        <v>78813</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135821162</v>
       </c>
       <c r="B25" t="n">
-        <v>78809</v>
+        <v>78813</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>135821167</v>
       </c>
       <c r="B26" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>135821171</v>
       </c>
       <c r="B27" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135821158</v>
       </c>
       <c r="B28" t="n">
-        <v>93061</v>
+        <v>93067</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>135821177</v>
       </c>
       <c r="B29" t="n">
-        <v>96723</v>
+        <v>96734</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>135821160</v>
       </c>
       <c r="B30" t="n">
-        <v>87709</v>
+        <v>87715</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 16081-2026 artfynd.xlsx
+++ b/artfynd/A 16081-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135821154</v>
       </c>
       <c r="B2" t="n">
-        <v>93396</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135821163</v>
       </c>
       <c r="B3" t="n">
-        <v>78463</v>
+        <v>78469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135821174</v>
       </c>
       <c r="B4" t="n">
-        <v>97973</v>
+        <v>97986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135821176</v>
       </c>
       <c r="B5" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>135821189</v>
       </c>
       <c r="B6" t="n">
-        <v>97411</v>
+        <v>97424</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135821166</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>135821173</v>
       </c>
       <c r="B8" t="n">
-        <v>79613</v>
+        <v>79619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135821170</v>
       </c>
       <c r="B9" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>135821175</v>
       </c>
       <c r="B10" t="n">
-        <v>79613</v>
+        <v>79619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>135821178</v>
       </c>
       <c r="B11" t="n">
-        <v>78813</v>
+        <v>78819</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135821161</v>
       </c>
       <c r="B12" t="n">
-        <v>89446</v>
+        <v>89453</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>135821155</v>
       </c>
       <c r="B13" t="n">
-        <v>79613</v>
+        <v>79619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>135821156</v>
       </c>
       <c r="B14" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>135821179</v>
       </c>
       <c r="B15" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135821157</v>
       </c>
       <c r="B16" t="n">
-        <v>78813</v>
+        <v>78819</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>135821165</v>
       </c>
       <c r="B17" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>135821168</v>
       </c>
       <c r="B18" t="n">
-        <v>93050</v>
+        <v>93057</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>135821169</v>
       </c>
       <c r="B19" t="n">
-        <v>41613</v>
+        <v>41618</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>135821180</v>
       </c>
       <c r="B20" t="n">
-        <v>79613</v>
+        <v>79619</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>135821164</v>
       </c>
       <c r="B21" t="n">
-        <v>83446</v>
+        <v>83452</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>135821152</v>
       </c>
       <c r="B22" t="n">
-        <v>83439</v>
+        <v>83445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>135821159</v>
       </c>
       <c r="B23" t="n">
-        <v>79535</v>
+        <v>79541</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>135821153</v>
       </c>
       <c r="B24" t="n">
-        <v>78813</v>
+        <v>78819</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135821162</v>
       </c>
       <c r="B25" t="n">
-        <v>78813</v>
+        <v>78819</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>135821167</v>
       </c>
       <c r="B26" t="n">
-        <v>79613</v>
+        <v>79619</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>135821171</v>
       </c>
       <c r="B27" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135821158</v>
       </c>
       <c r="B28" t="n">
-        <v>93067</v>
+        <v>93074</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>135821177</v>
       </c>
       <c r="B29" t="n">
-        <v>96734</v>
+        <v>96747</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>135821160</v>
       </c>
       <c r="B30" t="n">
-        <v>87715</v>
+        <v>87722</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 16081-2026 artfynd.xlsx
+++ b/artfynd/A 16081-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135821154</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135821174</v>
       </c>
       <c r="B4" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>135821189</v>
       </c>
       <c r="B6" t="n">
-        <v>97424</v>
+        <v>97425</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135821161</v>
       </c>
       <c r="B12" t="n">
-        <v>89453</v>
+        <v>89454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>135821168</v>
       </c>
       <c r="B18" t="n">
-        <v>93057</v>
+        <v>93058</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135821158</v>
       </c>
       <c r="B28" t="n">
-        <v>93074</v>
+        <v>93075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>135821177</v>
       </c>
       <c r="B29" t="n">
-        <v>96747</v>
+        <v>96748</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 16081-2026 artfynd.xlsx
+++ b/artfynd/A 16081-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135821154</v>
       </c>
       <c r="B2" t="n">
-        <v>93404</v>
+        <v>93417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135821163</v>
       </c>
       <c r="B3" t="n">
-        <v>78469</v>
+        <v>78482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135821174</v>
       </c>
       <c r="B4" t="n">
-        <v>97987</v>
+        <v>98000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135821176</v>
       </c>
       <c r="B5" t="n">
-        <v>83447</v>
+        <v>83460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>135821189</v>
       </c>
       <c r="B6" t="n">
-        <v>97425</v>
+        <v>97438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135821166</v>
       </c>
       <c r="B7" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>135821173</v>
       </c>
       <c r="B8" t="n">
-        <v>79619</v>
+        <v>79632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135821170</v>
       </c>
       <c r="B9" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>135821175</v>
       </c>
       <c r="B10" t="n">
-        <v>79619</v>
+        <v>79632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>135821178</v>
       </c>
       <c r="B11" t="n">
-        <v>78819</v>
+        <v>78832</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135821161</v>
       </c>
       <c r="B12" t="n">
-        <v>89454</v>
+        <v>89467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>135821155</v>
       </c>
       <c r="B13" t="n">
-        <v>79619</v>
+        <v>79632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>135821156</v>
       </c>
       <c r="B14" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>135821179</v>
       </c>
       <c r="B15" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135821157</v>
       </c>
       <c r="B16" t="n">
-        <v>78819</v>
+        <v>78832</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>135821165</v>
       </c>
       <c r="B17" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>135821168</v>
       </c>
       <c r="B18" t="n">
-        <v>93058</v>
+        <v>93071</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>135821169</v>
       </c>
       <c r="B19" t="n">
-        <v>41618</v>
+        <v>41631</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>135821180</v>
       </c>
       <c r="B20" t="n">
-        <v>79619</v>
+        <v>79632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>135821164</v>
       </c>
       <c r="B21" t="n">
-        <v>83452</v>
+        <v>83465</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>135821152</v>
       </c>
       <c r="B22" t="n">
-        <v>83445</v>
+        <v>83458</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>135821159</v>
       </c>
       <c r="B23" t="n">
-        <v>79541</v>
+        <v>79554</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>135821153</v>
       </c>
       <c r="B24" t="n">
-        <v>78819</v>
+        <v>78832</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>135821162</v>
       </c>
       <c r="B25" t="n">
-        <v>78819</v>
+        <v>78832</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>135821167</v>
       </c>
       <c r="B26" t="n">
-        <v>79619</v>
+        <v>79632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>135821171</v>
       </c>
       <c r="B27" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135821158</v>
       </c>
       <c r="B28" t="n">
-        <v>93075</v>
+        <v>93088</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>135821177</v>
       </c>
       <c r="B29" t="n">
-        <v>96748</v>
+        <v>96761</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>135821160</v>
       </c>
       <c r="B30" t="n">
-        <v>87722</v>
+        <v>87735</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 16081-2026 artfynd.xlsx
+++ b/artfynd/A 16081-2026 artfynd.xlsx
@@ -1116,7 +1116,7 @@
         <v>135821189</v>
       </c>
       <c r="B6" t="n">
-        <v>97438</v>
+        <v>97439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
